--- a/test/integration/04-out.xlsx
+++ b/test/integration/04-out.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="362">
   <si>
     <t>variable</t>
   </si>
@@ -27,6 +27,9 @@
   </si>
   <si>
     <t>name</t>
+  </si>
+  <si>
+    <t>method</t>
   </si>
   <si>
     <t>Buğday, Durum Buğdayı Hariç</t>
@@ -530,9 +533,6 @@
     <t>Koyunculuk</t>
   </si>
   <si>
-    <t>{}</t>
-  </si>
-  <si>
     <t>constraint</t>
   </si>
   <si>
@@ -542,10 +542,49 @@
     <t>rhs</t>
   </si>
   <si>
-    <t>Toplam Arazi</t>
+    <t>&lt;=</t>
   </si>
   <si>
-    <t>&lt;=</t>
+    <t>code</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>OPTIMAL</t>
+  </si>
+  <si>
+    <t>Solution is optimal</t>
+  </si>
+  <si>
+    <t>reduced_cost</t>
+  </si>
+  <si>
+    <t>original_value</t>
+  </si>
+  <si>
+    <t>lower_bound</t>
+  </si>
+  <si>
+    <t>upper_bound</t>
+  </si>
+  <si>
+    <t>is_basic_variable</t>
+  </si>
+  <si>
+    <t>shadow_price</t>
+  </si>
+  <si>
+    <t>slack_or_surplus</t>
+  </si>
+  <si>
+    <t>neither_bounds_are_binding</t>
+  </si>
+  <si>
+    <t>Toplam Arazi</t>
   </si>
   <si>
     <t>Toplam Kuru Tarla Arazisi</t>
@@ -1066,45 +1105,6 @@
   <si>
     <t>Ağıl Yeri</t>
   </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>OPTIMAL</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>Solution is optimal</t>
-  </si>
-  <si>
-    <t>reduced_cost</t>
-  </si>
-  <si>
-    <t>original_value</t>
-  </si>
-  <si>
-    <t>lower_bound</t>
-  </si>
-  <si>
-    <t>upper_bound</t>
-  </si>
-  <si>
-    <t>is_basic_variable</t>
-  </si>
-  <si>
-    <t>shadow_price</t>
-  </si>
-  <si>
-    <t>slack_or_surplus</t>
-  </si>
-  <si>
-    <t>neither_bounds_are_binding</t>
-  </si>
 </sst>
 </file>
 
@@ -1435,15 +1435,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C168"/>
+  <dimension ref="A1:D168"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="33.42578125" customWidth="1"/>
     <col min="2" max="2" width="10.5703125" customWidth="1"/>
     <col min="3" max="3" width="4.42578125" customWidth="1"/>
+    <col min="4" max="4" width="6.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1453,125 +1454,125 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>-324.12</v>
       </c>
-      <c r="C2" t="s">
-        <v>170</v>
-      </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>2.73</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>-839.12</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>2.73</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>-1439.82</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>2.6</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>-292.92</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>2.5</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>-721.12</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11">
         <v>2.5</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>-253.62</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>2.63</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14">
         <v>-245.55</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16">
         <v>-311.42</v>
@@ -1579,7 +1580,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17">
         <v>2.35</v>
@@ -1587,7 +1588,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18">
         <v>-923.5599999999999</v>
@@ -1595,7 +1596,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19">
         <v>1.1</v>
@@ -1603,7 +1604,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20">
         <v>-1935.27</v>
@@ -1611,7 +1612,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21">
         <v>2.5</v>
@@ -1619,7 +1620,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B22">
         <v>-522.39</v>
@@ -1627,7 +1628,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B23">
         <v>5.5</v>
@@ -1635,7 +1636,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B24">
         <v>-1022.54</v>
@@ -1643,7 +1644,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B25">
         <v>50</v>
@@ -1651,7 +1652,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B26">
         <v>-139.4</v>
@@ -1659,7 +1660,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B27">
         <v>1.3</v>
@@ -1667,7 +1668,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B28">
         <v>-2035.67</v>
@@ -1675,7 +1676,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29">
         <v>0.48</v>
@@ -1683,7 +1684,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30">
         <v>-469.64</v>
@@ -1691,7 +1692,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -1699,7 +1700,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B32">
         <v>-426</v>
@@ -1707,7 +1708,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -1715,7 +1716,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B34">
         <v>-458.96</v>
@@ -1723,7 +1724,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B35">
         <v>0.3</v>
@@ -1731,7 +1732,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B36">
         <v>-1323.15</v>
@@ -1739,7 +1740,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B37">
         <v>0.4</v>
@@ -1747,7 +1748,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B38">
         <v>-235.45</v>
@@ -1755,7 +1756,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -1763,7 +1764,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B40">
         <v>-704.35</v>
@@ -1771,7 +1772,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B41">
         <v>1.1</v>
@@ -1779,7 +1780,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B42">
         <v>-1542.22</v>
@@ -1787,7 +1788,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -1795,7 +1796,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B44">
         <v>-2062.33</v>
@@ -1803,7 +1804,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B45">
         <v>15</v>
@@ -1811,7 +1812,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B46">
         <v>-1524.22</v>
@@ -1819,7 +1820,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B47">
         <v>3</v>
@@ -1827,7 +1828,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B48">
         <v>-4731.46</v>
@@ -1835,7 +1836,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B49">
         <v>1.24</v>
@@ -1843,7 +1844,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B50">
         <v>-4564.14</v>
@@ -1851,7 +1852,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B51">
         <v>1.4</v>
@@ -1859,7 +1860,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B52">
         <v>-2800.16</v>
@@ -1867,7 +1868,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B53">
         <v>4.75</v>
@@ -1875,7 +1876,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B54">
         <v>-1201.23</v>
@@ -1883,7 +1884,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B55">
         <v>4</v>
@@ -1891,7 +1892,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B56">
         <v>-1012.14</v>
@@ -1899,7 +1900,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B57">
         <v>4</v>
@@ -1907,7 +1908,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B58">
         <v>-2546.56</v>
@@ -1915,7 +1916,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B59">
         <v>4.33</v>
@@ -1923,7 +1924,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B60">
         <v>-2710.05</v>
@@ -1931,7 +1932,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -1939,7 +1940,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B62">
         <v>-2166.68</v>
@@ -1947,7 +1948,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B63">
         <v>1</v>
@@ -1955,7 +1956,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B64">
         <v>-8502.950000000001</v>
@@ -1963,7 +1964,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B65">
         <v>2.3</v>
@@ -1971,7 +1972,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B66">
         <v>-5892.95</v>
@@ -1979,7 +1980,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B67">
         <v>2.6</v>
@@ -1987,7 +1988,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B68">
         <v>-7597.45</v>
@@ -1995,7 +1996,7 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B69">
         <v>2.2</v>
@@ -2003,7 +2004,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B70">
         <v>-6173.95</v>
@@ -2011,7 +2012,7 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B71">
         <v>1.7</v>
@@ -2019,7 +2020,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B72">
         <v>-1640.96</v>
@@ -2027,7 +2028,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B73">
         <v>2</v>
@@ -2035,7 +2036,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B74">
         <v>-5458.56</v>
@@ -2043,7 +2044,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B75">
         <v>15</v>
@@ -2051,7 +2052,7 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B76">
         <v>-3383.5</v>
@@ -2059,7 +2060,7 @@
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B77">
         <v>10</v>
@@ -2067,7 +2068,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B78">
         <v>-2033.1</v>
@@ -2075,7 +2076,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B79">
         <v>0.7</v>
@@ -2083,7 +2084,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B80">
         <v>-2619.5</v>
@@ -2091,7 +2092,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B81">
         <v>4</v>
@@ -2099,7 +2100,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B82">
         <v>-3546.89</v>
@@ -2107,7 +2108,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B83">
         <v>4</v>
@@ -2115,7 +2116,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B84">
         <v>-1045.56</v>
@@ -2123,7 +2124,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B85">
         <v>2</v>
@@ -2131,7 +2132,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B86">
         <v>-3040</v>
@@ -2139,7 +2140,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B87">
         <v>2.3</v>
@@ -2147,7 +2148,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B88">
         <v>-1004.65</v>
@@ -2155,7 +2156,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B89">
         <v>4</v>
@@ -2163,7 +2164,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B90">
         <v>-3040</v>
@@ -2171,7 +2172,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B91">
         <v>2.2</v>
@@ -2179,7 +2180,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B92">
         <v>-1346.3</v>
@@ -2187,7 +2188,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B93">
         <v>8</v>
@@ -2195,7 +2196,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B94">
         <v>-928.25</v>
@@ -2203,7 +2204,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B95">
         <v>6</v>
@@ -2211,7 +2212,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B96">
         <v>-2090</v>
@@ -2219,7 +2220,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B97">
         <v>2.5</v>
@@ -2227,7 +2228,7 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B98">
         <v>-7030</v>
@@ -2235,7 +2236,7 @@
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B99">
         <v>6</v>
@@ -2243,7 +2244,7 @@
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B100">
         <v>-2090</v>
@@ -2251,7 +2252,7 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B101">
         <v>2.3</v>
@@ -2259,7 +2260,7 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B102">
         <v>-1514</v>
@@ -2267,7 +2268,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B103">
         <v>4.25</v>
@@ -2275,7 +2276,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B104">
         <v>-874.66</v>
@@ -2283,7 +2284,7 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B105">
         <v>10</v>
@@ -2291,7 +2292,7 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B106">
         <v>-1542.23</v>
@@ -2299,7 +2300,7 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B107">
         <v>10</v>
@@ -2307,7 +2308,7 @@
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B108">
         <v>-1524.56</v>
@@ -2315,7 +2316,7 @@
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B109">
         <v>3</v>
@@ -2323,7 +2324,7 @@
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B110">
         <v>-5720</v>
@@ -2331,7 +2332,7 @@
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B111">
         <v>15</v>
@@ -2339,7 +2340,7 @@
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B112">
         <v>-358.45</v>
@@ -2347,7 +2348,7 @@
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -2355,7 +2356,7 @@
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B114">
         <v>-232.7</v>
@@ -2363,7 +2364,7 @@
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B115">
         <v>2</v>
@@ -2371,7 +2372,7 @@
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B116">
         <v>-408.7</v>
@@ -2379,7 +2380,7 @@
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B117">
         <v>0.6</v>
@@ -2387,7 +2388,7 @@
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B118">
         <v>-1344.71</v>
@@ -2395,7 +2396,7 @@
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B119">
         <v>19.5</v>
@@ -2403,7 +2404,7 @@
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B120">
         <v>-2090</v>
@@ -2411,7 +2412,7 @@
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B121">
         <v>2.5</v>
@@ -2419,7 +2420,7 @@
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B122">
         <v>-515.3</v>
@@ -2427,7 +2428,7 @@
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B123">
         <v>15</v>
@@ -2435,7 +2436,7 @@
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B124">
         <v>-364.85</v>
@@ -2443,7 +2444,7 @@
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B125">
         <v>7</v>
@@ -2451,7 +2452,7 @@
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B126">
         <v>-276.95</v>
@@ -2459,7 +2460,7 @@
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B127">
         <v>6.5</v>
@@ -2467,7 +2468,7 @@
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B128">
         <v>-1834</v>
@@ -2475,7 +2476,7 @@
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B129">
         <v>6</v>
@@ -2483,7 +2484,7 @@
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B130">
         <v>-152.24</v>
@@ -2491,7 +2492,7 @@
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -2499,7 +2500,7 @@
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B132">
         <v>-3653.69</v>
@@ -2507,7 +2508,7 @@
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B133">
         <v>1.2</v>
@@ -2515,7 +2516,7 @@
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B134">
         <v>-982.14</v>
@@ -2523,7 +2524,7 @@
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B135">
         <v>1.6</v>
@@ -2531,7 +2532,7 @@
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B136">
         <v>-1115.45</v>
@@ -2539,7 +2540,7 @@
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B137">
         <v>3</v>
@@ -2547,7 +2548,7 @@
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B138">
         <v>-120.25</v>
@@ -2555,7 +2556,7 @@
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B139">
         <v>1.3</v>
@@ -2563,7 +2564,7 @@
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B140">
         <v>-821.15</v>
@@ -2571,7 +2572,7 @@
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B141">
         <v>5.5</v>
@@ -2579,7 +2580,7 @@
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B142">
         <v>-858.45</v>
@@ -2587,7 +2588,7 @@
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B143">
         <v>8.109999999999999</v>
@@ -2595,7 +2596,7 @@
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B144">
         <v>-684.45</v>
@@ -2603,7 +2604,7 @@
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B145">
         <v>2.35</v>
@@ -2611,7 +2612,7 @@
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B146">
         <v>-450.25</v>
@@ -2619,7 +2620,7 @@
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B147">
         <v>7</v>
@@ -2627,7 +2628,7 @@
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B148">
         <v>-1847.87</v>
@@ -2635,7 +2636,7 @@
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B149">
         <v>8.109999999999999</v>
@@ -2643,7 +2644,7 @@
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B150">
         <v>-678.45</v>
@@ -2651,7 +2652,7 @@
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B151">
         <v>2.63</v>
@@ -2659,7 +2660,7 @@
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B152">
         <v>-598.9</v>
@@ -2667,7 +2668,7 @@
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B153">
         <v>6.3</v>
@@ -2675,7 +2676,7 @@
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B154">
         <v>-18.75</v>
@@ -2683,7 +2684,7 @@
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B155">
         <v>-18.75</v>
@@ -2691,7 +2692,7 @@
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B156">
         <v>-18.75</v>
@@ -2699,7 +2700,7 @@
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B157">
         <v>-18.75</v>
@@ -2707,7 +2708,7 @@
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B158">
         <v>-18.75</v>
@@ -2715,7 +2716,7 @@
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B159">
         <v>-18.75</v>
@@ -2723,7 +2724,7 @@
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B160">
         <v>-18.75</v>
@@ -2731,7 +2732,7 @@
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B161">
         <v>-18.75</v>
@@ -2739,7 +2740,7 @@
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B162">
         <v>-18.75</v>
@@ -2747,7 +2748,7 @@
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B163">
         <v>-18.75</v>
@@ -2755,7 +2756,7 @@
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B164">
         <v>-18.75</v>
@@ -2763,7 +2764,7 @@
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B165">
         <v>-18.75</v>
@@ -2771,7 +2772,7 @@
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B166">
         <v>-0.25</v>
@@ -2779,7 +2780,7 @@
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B167">
         <v>5014</v>
@@ -2787,7 +2788,7 @@
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B168">
         <v>977</v>
@@ -2803,7 +2804,7 @@
   <dimension ref="A1:FN175"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="36.140625" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="3.5703125" customWidth="1"/>
     <col min="4" max="4" width="24.7109375" customWidth="1"/>
@@ -2986,513 +2987,510 @@
         <v>173</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AD1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AF1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AG1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AH1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AI1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AJ1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AK1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AL1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AM1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AN1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AO1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AP1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AQ1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AR1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AS1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AT1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AU1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AV1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AW1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AX1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AY1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AZ1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="BA1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="BB1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="BC1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="BD1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="BE1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="BF1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="BG1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="BH1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="BI1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="BJ1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="BK1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="BL1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="BM1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="BN1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="BO1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="BP1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="BQ1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="BR1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="BS1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="BT1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="BU1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="BV1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="BW1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BX1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BY1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="BZ1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="CA1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="CB1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="CC1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="CD1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="CE1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="CF1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="CG1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="CH1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="CI1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="CJ1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="CK1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="CL1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="CM1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="CN1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="CO1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="CP1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="CQ1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="CR1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="CS1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="CT1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="CU1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="CV1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="CW1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="CX1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="CY1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="CZ1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="DA1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="DB1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="DC1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="DD1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="DE1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="DF1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="DG1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="DH1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="DI1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="DJ1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="DK1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="DL1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="DM1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="DN1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="DO1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="DP1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="DQ1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="DR1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="DS1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="DT1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="DU1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="DV1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="DW1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="DX1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="DY1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="DZ1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="EA1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="EB1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="EC1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="ED1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="EE1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="EF1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="EG1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="EH1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="EI1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="EJ1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="EK1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="EL1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="EM1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="EN1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="EO1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="EP1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="EQ1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="ER1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="ES1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="ET1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="EU1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="EV1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="EW1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="EX1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="EY1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="EZ1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="FA1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="FB1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="FC1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="FD1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="FE1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="FF1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="FG1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="FH1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="FI1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="FJ1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="FK1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="FL1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="FM1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="FN1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:170">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>174</v>
-      </c>
-      <c r="B2" t="s">
-        <v>175</v>
       </c>
       <c r="C2">
         <v>5508331</v>
@@ -4000,11 +3998,8 @@
       </c>
     </row>
     <row r="3" spans="1:170">
-      <c r="A3" t="s">
-        <v>176</v>
-      </c>
       <c r="B3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C3">
         <v>2660003</v>
@@ -4512,11 +4507,8 @@
       </c>
     </row>
     <row r="4" spans="1:170">
-      <c r="A4" t="s">
-        <v>177</v>
-      </c>
       <c r="B4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C4">
         <v>1013373</v>
@@ -5024,11 +5016,8 @@
       </c>
     </row>
     <row r="5" spans="1:170">
-      <c r="A5" t="s">
-        <v>178</v>
-      </c>
       <c r="B5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C5">
         <v>154013</v>
@@ -5536,11 +5525,8 @@
       </c>
     </row>
     <row r="6" spans="1:170">
-      <c r="A6" t="s">
-        <v>179</v>
-      </c>
       <c r="B6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C6">
         <v>397158</v>
@@ -6048,11 +6034,8 @@
       </c>
     </row>
     <row r="7" spans="1:170">
-      <c r="A7" t="s">
-        <v>180</v>
-      </c>
       <c r="B7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C7">
         <v>4.8</v>
@@ -6560,11 +6543,8 @@
       </c>
     </row>
     <row r="8" spans="1:170">
-      <c r="A8" t="s">
-        <v>181</v>
-      </c>
       <c r="B8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -7072,11 +7052,8 @@
       </c>
     </row>
     <row r="9" spans="1:170">
-      <c r="A9" t="s">
-        <v>182</v>
-      </c>
       <c r="B9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C9">
         <v>2189475</v>
@@ -7584,11 +7561,8 @@
       </c>
     </row>
     <row r="10" spans="1:170">
-      <c r="A10" t="s">
-        <v>183</v>
-      </c>
       <c r="B10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C10">
         <v>279382.5</v>
@@ -8096,11 +8070,8 @@
       </c>
     </row>
     <row r="11" spans="1:170">
-      <c r="A11" t="s">
-        <v>184</v>
-      </c>
       <c r="B11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C11">
         <v>13156.5</v>
@@ -8608,11 +8579,8 @@
       </c>
     </row>
     <row r="12" spans="1:170">
-      <c r="A12" t="s">
-        <v>185</v>
-      </c>
       <c r="B12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C12">
         <v>1359679.5</v>
@@ -9120,11 +9088,8 @@
       </c>
     </row>
     <row r="13" spans="1:170">
-      <c r="A13" t="s">
-        <v>186</v>
-      </c>
       <c r="B13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C13">
         <v>87864</v>
@@ -9632,11 +9597,8 @@
       </c>
     </row>
     <row r="14" spans="1:170">
-      <c r="A14" t="s">
-        <v>187</v>
-      </c>
       <c r="B14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C14">
         <v>28324.5</v>
@@ -10144,11 +10106,8 @@
       </c>
     </row>
     <row r="15" spans="1:170">
-      <c r="A15" t="s">
-        <v>188</v>
-      </c>
       <c r="B15" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C15">
         <v>35854.5</v>
@@ -10656,11 +10615,8 @@
       </c>
     </row>
     <row r="16" spans="1:170">
-      <c r="A16" t="s">
-        <v>189</v>
-      </c>
       <c r="B16" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C16">
         <v>31813.5</v>
@@ -11167,12 +11123,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:170">
-      <c r="A17" t="s">
-        <v>190</v>
-      </c>
+    <row r="17" spans="2:170">
       <c r="B17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C17">
         <v>550</v>
@@ -11679,12 +11632,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:170">
-      <c r="A18" t="s">
-        <v>191</v>
-      </c>
+    <row r="18" spans="2:170">
       <c r="B18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C18">
         <v>1962</v>
@@ -12191,12 +12141,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:170">
-      <c r="A19" t="s">
-        <v>192</v>
-      </c>
+    <row r="19" spans="2:170">
       <c r="B19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C19">
         <v>5076</v>
@@ -12703,12 +12650,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:170">
-      <c r="A20" t="s">
-        <v>193</v>
-      </c>
+    <row r="20" spans="2:170">
       <c r="B20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C20">
         <v>72.60000000000001</v>
@@ -13215,12 +13159,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:170">
-      <c r="A21" t="s">
-        <v>194</v>
-      </c>
+    <row r="21" spans="2:170">
       <c r="B21" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C21">
         <v>17860.7</v>
@@ -13727,12 +13668,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:170">
-      <c r="A22" t="s">
-        <v>195</v>
-      </c>
+    <row r="22" spans="2:170">
       <c r="B22" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C22">
         <v>207465</v>
@@ -14239,12 +14177,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:170">
-      <c r="A23" t="s">
-        <v>196</v>
-      </c>
+    <row r="23" spans="2:170">
       <c r="B23" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C23">
         <v>113121</v>
@@ -14751,12 +14686,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:170">
-      <c r="A24" t="s">
-        <v>197</v>
-      </c>
+    <row r="24" spans="2:170">
       <c r="B24" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C24">
         <v>24649.9</v>
@@ -15263,12 +15195,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:170">
-      <c r="A25" t="s">
-        <v>198</v>
-      </c>
+    <row r="25" spans="2:170">
       <c r="B25" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C25">
         <v>66</v>
@@ -15775,12 +15704,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:170">
-      <c r="A26" t="s">
-        <v>199</v>
-      </c>
+    <row r="26" spans="2:170">
       <c r="B26" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C26">
         <v>116017.5</v>
@@ -16287,12 +16213,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:170">
-      <c r="A27" t="s">
-        <v>200</v>
-      </c>
+    <row r="27" spans="2:170">
       <c r="B27" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C27">
         <v>25470.5</v>
@@ -16799,12 +16722,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:170">
-      <c r="A28" t="s">
-        <v>201</v>
-      </c>
+    <row r="28" spans="2:170">
       <c r="B28" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C28">
         <v>4867.5</v>
@@ -17311,12 +17231,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:170">
-      <c r="A29" t="s">
-        <v>202</v>
-      </c>
+    <row r="29" spans="2:170">
       <c r="B29" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C29">
         <v>30.8</v>
@@ -17823,12 +17740,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:170">
-      <c r="A30" t="s">
-        <v>203</v>
-      </c>
+    <row r="30" spans="2:170">
       <c r="B30" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C30">
         <v>27.3</v>
@@ -18335,12 +18249,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:170">
-      <c r="A31" t="s">
-        <v>204</v>
-      </c>
+    <row r="31" spans="2:170">
       <c r="B31" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C31">
         <v>2</v>
@@ -18847,12 +18758,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:170">
-      <c r="A32" t="s">
-        <v>205</v>
-      </c>
+    <row r="32" spans="2:170">
       <c r="B32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C32">
         <v>160.6</v>
@@ -19359,12 +19267,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:170">
-      <c r="A33" t="s">
-        <v>206</v>
-      </c>
+    <row r="33" spans="2:170">
       <c r="B33" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C33">
         <v>186</v>
@@ -19871,12 +19776,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:170">
-      <c r="A34" t="s">
-        <v>207</v>
-      </c>
+    <row r="34" spans="2:170">
       <c r="B34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C34">
         <v>258</v>
@@ -20383,12 +20285,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:170">
-      <c r="A35" t="s">
-        <v>208</v>
-      </c>
+    <row r="35" spans="2:170">
       <c r="B35" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C35">
         <v>62.4</v>
@@ -20895,12 +20794,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:170">
-      <c r="A36" t="s">
-        <v>209</v>
-      </c>
+    <row r="36" spans="2:170">
       <c r="B36" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C36">
         <v>14.4</v>
@@ -21407,12 +21303,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:170">
-      <c r="A37" t="s">
-        <v>210</v>
-      </c>
+    <row r="37" spans="2:170">
       <c r="B37" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C37">
         <v>6</v>
@@ -21919,12 +21812,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:170">
-      <c r="A38" t="s">
-        <v>211</v>
-      </c>
+    <row r="38" spans="2:170">
       <c r="B38" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C38">
         <v>4992</v>
@@ -22431,12 +22321,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:170">
-      <c r="A39" t="s">
-        <v>212</v>
-      </c>
+    <row r="39" spans="2:170">
       <c r="B39" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C39">
         <v>1614</v>
@@ -22943,12 +22830,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:170">
-      <c r="A40" t="s">
-        <v>213</v>
-      </c>
+    <row r="40" spans="2:170">
       <c r="B40" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C40">
         <v>922.9000000000001</v>
@@ -23455,12 +23339,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:170">
-      <c r="A41" t="s">
-        <v>214</v>
-      </c>
+    <row r="41" spans="2:170">
       <c r="B41" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C41">
         <v>1101.1</v>
@@ -23967,12 +23848,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:170">
-      <c r="A42" t="s">
-        <v>215</v>
-      </c>
+    <row r="42" spans="2:170">
       <c r="B42" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C42">
         <v>957.0000000000001</v>
@@ -24479,12 +24357,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:170">
-      <c r="A43" t="s">
-        <v>216</v>
-      </c>
+    <row r="43" spans="2:170">
       <c r="B43" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C43">
         <v>12311.2</v>
@@ -24991,12 +24866,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:170">
-      <c r="A44" t="s">
-        <v>217</v>
-      </c>
+    <row r="44" spans="2:170">
       <c r="B44" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C44">
         <v>22</v>
@@ -25503,12 +25375,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:170">
-      <c r="A45" t="s">
-        <v>218</v>
-      </c>
+    <row r="45" spans="2:170">
       <c r="B45" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C45">
         <v>189.8</v>
@@ -26015,12 +25884,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:170">
-      <c r="A46" t="s">
-        <v>219</v>
-      </c>
+    <row r="46" spans="2:170">
       <c r="B46" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C46">
         <v>131.3</v>
@@ -26527,12 +26393,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:170">
-      <c r="A47" t="s">
-        <v>220</v>
-      </c>
+    <row r="47" spans="2:170">
       <c r="B47" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C47">
         <v>605.8000000000001</v>
@@ -27039,12 +26902,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:170">
-      <c r="A48" t="s">
-        <v>221</v>
-      </c>
+    <row r="48" spans="2:170">
       <c r="B48" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C48">
         <v>536.9</v>
@@ -27551,12 +27411,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:170">
-      <c r="A49" t="s">
-        <v>222</v>
-      </c>
+    <row r="49" spans="2:170">
       <c r="B49" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C49">
         <v>146.9</v>
@@ -28063,12 +27920,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:170">
-      <c r="A50" t="s">
-        <v>223</v>
-      </c>
+    <row r="50" spans="2:170">
       <c r="B50" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C50">
         <v>37</v>
@@ -28575,12 +28429,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:170">
-      <c r="A51" t="s">
-        <v>224</v>
-      </c>
+    <row r="51" spans="2:170">
       <c r="B51" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C51">
         <v>72783</v>
@@ -29087,12 +28938,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:170">
-      <c r="A52" t="s">
-        <v>225</v>
-      </c>
+    <row r="52" spans="2:170">
       <c r="B52" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C52">
         <v>686</v>
@@ -29599,12 +29447,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:170">
-      <c r="A53" t="s">
-        <v>226</v>
-      </c>
+    <row r="53" spans="2:170">
       <c r="B53" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -30111,12 +29956,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:170">
-      <c r="A54" t="s">
-        <v>227</v>
-      </c>
+    <row r="54" spans="2:170">
       <c r="B54" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C54">
         <v>743</v>
@@ -30623,12 +30465,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:170">
-      <c r="A55" t="s">
-        <v>228</v>
-      </c>
+    <row r="55" spans="2:170">
       <c r="B55" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C55">
         <v>172</v>
@@ -31135,12 +30974,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:170">
-      <c r="A56" t="s">
-        <v>229</v>
-      </c>
+    <row r="56" spans="2:170">
       <c r="B56" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C56">
         <v>250</v>
@@ -31647,12 +31483,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:170">
-      <c r="A57" t="s">
-        <v>230</v>
-      </c>
+    <row r="57" spans="2:170">
       <c r="B57" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C57">
         <v>685</v>
@@ -32159,12 +31992,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:170">
-      <c r="A58" t="s">
-        <v>231</v>
-      </c>
+    <row r="58" spans="2:170">
       <c r="B58" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C58">
         <v>125</v>
@@ -32671,12 +32501,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:170">
-      <c r="A59" t="s">
-        <v>232</v>
-      </c>
+    <row r="59" spans="2:170">
       <c r="B59" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C59">
         <v>3441</v>
@@ -33183,12 +33010,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:170">
-      <c r="A60" t="s">
-        <v>233</v>
-      </c>
+    <row r="60" spans="2:170">
       <c r="B60" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C60">
         <v>440.0000000000001</v>
@@ -33695,12 +33519,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:170">
-      <c r="A61" t="s">
-        <v>234</v>
-      </c>
+    <row r="61" spans="2:170">
       <c r="B61" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C61">
         <v>4.8</v>
@@ -34207,12 +34028,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:170">
-      <c r="A62" t="s">
-        <v>235</v>
-      </c>
+    <row r="62" spans="2:170">
       <c r="B62" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C62">
         <v>11</v>
@@ -34719,12 +34537,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:170">
-      <c r="A63" t="s">
-        <v>236</v>
-      </c>
+    <row r="63" spans="2:170">
       <c r="B63" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C63">
         <v>1804</v>
@@ -35231,12 +35046,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:170">
-      <c r="A64" t="s">
-        <v>237</v>
-      </c>
+    <row r="64" spans="2:170">
       <c r="B64" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C64">
         <v>421.3</v>
@@ -35743,12 +35555,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:170">
-      <c r="A65" t="s">
-        <v>238</v>
-      </c>
+    <row r="65" spans="2:170">
       <c r="B65" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C65">
         <v>165577.5</v>
@@ -36255,12 +36064,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:170">
-      <c r="A66" t="s">
-        <v>239</v>
-      </c>
+    <row r="66" spans="2:170">
       <c r="B66" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C66">
         <v>1800</v>
@@ -36767,12 +36573,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:170">
-      <c r="A67" t="s">
-        <v>240</v>
-      </c>
+    <row r="67" spans="2:170">
       <c r="B67" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C67">
         <v>559290</v>
@@ -37279,12 +37082,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:170">
-      <c r="A68" t="s">
-        <v>241</v>
-      </c>
+    <row r="68" spans="2:170">
       <c r="B68" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C68">
         <v>6399</v>
@@ -37791,12 +37591,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:170">
-      <c r="A69" t="s">
-        <v>242</v>
-      </c>
+    <row r="69" spans="2:170">
       <c r="B69" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C69">
         <v>3630</v>
@@ -38303,12 +38100,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:170">
-      <c r="A70" t="s">
-        <v>243</v>
-      </c>
+    <row r="70" spans="2:170">
       <c r="B70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C70">
         <v>3278.6</v>
@@ -38815,12 +38609,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:170">
-      <c r="A71" t="s">
-        <v>244</v>
-      </c>
+    <row r="71" spans="2:170">
       <c r="B71" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C71">
         <v>152080.5</v>
@@ -39327,12 +39118,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:170">
-      <c r="A72" t="s">
-        <v>245</v>
-      </c>
+    <row r="72" spans="2:170">
       <c r="B72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C72">
         <v>63194</v>
@@ -39839,12 +39627,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:170">
-      <c r="A73" t="s">
-        <v>246</v>
-      </c>
+    <row r="73" spans="2:170">
       <c r="B73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C73">
         <v>19.5</v>
@@ -40351,12 +40136,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:170">
-      <c r="A74" t="s">
-        <v>247</v>
-      </c>
+    <row r="74" spans="2:170">
       <c r="B74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C74">
         <v>176.07</v>
@@ -40863,12 +40645,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:170">
-      <c r="A75" t="s">
-        <v>248</v>
-      </c>
+    <row r="75" spans="2:170">
       <c r="B75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C75">
         <v>121915.2</v>
@@ -41375,12 +41154,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:170">
-      <c r="A76" t="s">
-        <v>249</v>
-      </c>
+    <row r="76" spans="2:170">
       <c r="B76" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C76">
         <v>30</v>
@@ -41887,12 +41663,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:170">
-      <c r="A77" t="s">
-        <v>250</v>
-      </c>
+    <row r="77" spans="2:170">
       <c r="B77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C77">
         <v>1342</v>
@@ -42399,12 +42172,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:170">
-      <c r="A78" t="s">
-        <v>251</v>
-      </c>
+    <row r="78" spans="2:170">
       <c r="B78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C78">
         <v>170789</v>
@@ -42911,12 +42681,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:170">
-      <c r="A79" t="s">
-        <v>252</v>
-      </c>
+    <row r="79" spans="2:170">
       <c r="B79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C79">
         <v>4123.6</v>
@@ -43423,12 +43190,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:170">
-      <c r="A80" t="s">
-        <v>253</v>
-      </c>
+    <row r="80" spans="2:170">
       <c r="B80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C80">
         <v>4599</v>
@@ -43935,12 +43699,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:170">
-      <c r="A81" t="s">
-        <v>254</v>
-      </c>
+    <row r="81" spans="2:170">
       <c r="B81" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C81">
         <v>33.8</v>
@@ -44447,12 +44208,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:170">
-      <c r="A82" t="s">
-        <v>255</v>
-      </c>
+    <row r="82" spans="2:170">
       <c r="B82" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C82">
         <v>42550.3</v>
@@ -44959,12 +44717,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:170">
-      <c r="A83" t="s">
-        <v>256</v>
-      </c>
+    <row r="83" spans="2:170">
       <c r="B83" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C83">
         <v>5968.5</v>
@@ -45471,12 +45226,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:170">
-      <c r="A84" t="s">
-        <v>257</v>
-      </c>
+    <row r="84" spans="2:170">
       <c r="B84" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C84">
         <v>2551.9</v>
@@ -45983,12 +45735,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:170">
-      <c r="A85" t="s">
-        <v>258</v>
-      </c>
+    <row r="85" spans="2:170">
       <c r="B85" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -46495,12 +46244,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:170">
-      <c r="A86" t="s">
-        <v>259</v>
-      </c>
+    <row r="86" spans="2:170">
       <c r="B86" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -47007,12 +46753,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:170">
-      <c r="A87" t="s">
-        <v>260</v>
-      </c>
+    <row r="87" spans="2:170">
       <c r="B87" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -47519,12 +47262,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:170">
-      <c r="A88" t="s">
-        <v>261</v>
-      </c>
+    <row r="88" spans="2:170">
       <c r="B88" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -48031,12 +47771,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:170">
-      <c r="A89" t="s">
-        <v>262</v>
-      </c>
+    <row r="89" spans="2:170">
       <c r="B89" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -48543,12 +48280,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:170">
-      <c r="A90" t="s">
-        <v>263</v>
-      </c>
+    <row r="90" spans="2:170">
       <c r="B90" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -49055,12 +48789,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:170">
-      <c r="A91" t="s">
-        <v>264</v>
-      </c>
+    <row r="91" spans="2:170">
       <c r="B91" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -49567,12 +49298,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:170">
-      <c r="A92" t="s">
-        <v>265</v>
-      </c>
+    <row r="92" spans="2:170">
       <c r="B92" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -50079,12 +49807,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:170">
-      <c r="A93" t="s">
-        <v>266</v>
-      </c>
+    <row r="93" spans="2:170">
       <c r="B93" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -50591,12 +50316,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:170">
-      <c r="A94" t="s">
-        <v>267</v>
-      </c>
+    <row r="94" spans="2:170">
       <c r="B94" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -51103,12 +50825,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:170">
-      <c r="A95" t="s">
-        <v>268</v>
-      </c>
+    <row r="95" spans="2:170">
       <c r="B95" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -51615,12 +51334,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:170">
-      <c r="A96" t="s">
-        <v>269</v>
-      </c>
+    <row r="96" spans="2:170">
       <c r="B96" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -52127,12 +51843,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:170">
-      <c r="A97" t="s">
-        <v>270</v>
-      </c>
+    <row r="97" spans="2:170">
       <c r="B97" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -52639,12 +52352,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:170">
-      <c r="A98" t="s">
-        <v>271</v>
-      </c>
+    <row r="98" spans="2:170">
       <c r="B98" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -53151,12 +52861,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:170">
-      <c r="A99" t="s">
-        <v>272</v>
-      </c>
+    <row r="99" spans="2:170">
       <c r="B99" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -53663,12 +53370,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:170">
-      <c r="A100" t="s">
-        <v>273</v>
-      </c>
+    <row r="100" spans="2:170">
       <c r="B100" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -54175,12 +53879,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:170">
-      <c r="A101" t="s">
-        <v>274</v>
-      </c>
+    <row r="101" spans="2:170">
       <c r="B101" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -54687,12 +54388,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:170">
-      <c r="A102" t="s">
-        <v>275</v>
-      </c>
+    <row r="102" spans="2:170">
       <c r="B102" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -55199,12 +54897,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:170">
-      <c r="A103" t="s">
-        <v>276</v>
-      </c>
+    <row r="103" spans="2:170">
       <c r="B103" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -55711,12 +55406,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:170">
-      <c r="A104" t="s">
-        <v>277</v>
-      </c>
+    <row r="104" spans="2:170">
       <c r="B104" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -56223,12 +55915,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:170">
-      <c r="A105" t="s">
-        <v>278</v>
-      </c>
+    <row r="105" spans="2:170">
       <c r="B105" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -56735,12 +56424,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:170">
-      <c r="A106" t="s">
-        <v>279</v>
-      </c>
+    <row r="106" spans="2:170">
       <c r="B106" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -57247,12 +56933,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:170">
-      <c r="A107" t="s">
-        <v>280</v>
-      </c>
+    <row r="107" spans="2:170">
       <c r="B107" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -57759,12 +57442,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:170">
-      <c r="A108" t="s">
-        <v>281</v>
-      </c>
+    <row r="108" spans="2:170">
       <c r="B108" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -58271,12 +57951,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:170">
-      <c r="A109" t="s">
-        <v>282</v>
-      </c>
+    <row r="109" spans="2:170">
       <c r="B109" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -58783,12 +58460,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:170">
-      <c r="A110" t="s">
-        <v>283</v>
-      </c>
+    <row r="110" spans="2:170">
       <c r="B110" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -59295,12 +58969,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:170">
-      <c r="A111" t="s">
-        <v>284</v>
-      </c>
+    <row r="111" spans="2:170">
       <c r="B111" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -59807,12 +59478,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:170">
-      <c r="A112" t="s">
-        <v>285</v>
-      </c>
+    <row r="112" spans="2:170">
       <c r="B112" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -60319,12 +59987,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:170">
-      <c r="A113" t="s">
-        <v>286</v>
-      </c>
+    <row r="113" spans="2:170">
       <c r="B113" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -60831,12 +60496,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:170">
-      <c r="A114" t="s">
-        <v>287</v>
-      </c>
+    <row r="114" spans="2:170">
       <c r="B114" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -61343,12 +61005,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:170">
-      <c r="A115" t="s">
-        <v>288</v>
-      </c>
+    <row r="115" spans="2:170">
       <c r="B115" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -61855,12 +61514,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:170">
-      <c r="A116" t="s">
-        <v>289</v>
-      </c>
+    <row r="116" spans="2:170">
       <c r="B116" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -62367,12 +62023,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:170">
-      <c r="A117" t="s">
-        <v>290</v>
-      </c>
+    <row r="117" spans="2:170">
       <c r="B117" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -62879,12 +62532,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:170">
-      <c r="A118" t="s">
-        <v>291</v>
-      </c>
+    <row r="118" spans="2:170">
       <c r="B118" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -63391,12 +63041,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:170">
-      <c r="A119" t="s">
-        <v>292</v>
-      </c>
+    <row r="119" spans="2:170">
       <c r="B119" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -63903,12 +63550,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:170">
-      <c r="A120" t="s">
-        <v>293</v>
-      </c>
+    <row r="120" spans="2:170">
       <c r="B120" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -64415,12 +64059,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:170">
-      <c r="A121" t="s">
-        <v>294</v>
-      </c>
+    <row r="121" spans="2:170">
       <c r="B121" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -64927,12 +64568,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:170">
-      <c r="A122" t="s">
-        <v>295</v>
-      </c>
+    <row r="122" spans="2:170">
       <c r="B122" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -65439,12 +65077,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:170">
-      <c r="A123" t="s">
-        <v>296</v>
-      </c>
+    <row r="123" spans="2:170">
       <c r="B123" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -65951,12 +65586,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:170">
-      <c r="A124" t="s">
-        <v>297</v>
-      </c>
+    <row r="124" spans="2:170">
       <c r="B124" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -66463,12 +66095,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:170">
-      <c r="A125" t="s">
-        <v>298</v>
-      </c>
+    <row r="125" spans="2:170">
       <c r="B125" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -66975,12 +66604,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:170">
-      <c r="A126" t="s">
-        <v>299</v>
-      </c>
+    <row r="126" spans="2:170">
       <c r="B126" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -67487,12 +67113,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:170">
-      <c r="A127" t="s">
-        <v>300</v>
-      </c>
+    <row r="127" spans="2:170">
       <c r="B127" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -67999,12 +67622,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:170">
-      <c r="A128" t="s">
-        <v>301</v>
-      </c>
+    <row r="128" spans="2:170">
       <c r="B128" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -68511,12 +68131,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:170">
-      <c r="A129" t="s">
-        <v>302</v>
-      </c>
+    <row r="129" spans="2:170">
       <c r="B129" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -69023,12 +68640,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:170">
-      <c r="A130" t="s">
-        <v>303</v>
-      </c>
+    <row r="130" spans="2:170">
       <c r="B130" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -69535,12 +69149,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:170">
-      <c r="A131" t="s">
-        <v>304</v>
-      </c>
+    <row r="131" spans="2:170">
       <c r="B131" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -70047,12 +69658,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:170">
-      <c r="A132" t="s">
-        <v>305</v>
-      </c>
+    <row r="132" spans="2:170">
       <c r="B132" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -70559,12 +70167,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:170">
-      <c r="A133" t="s">
-        <v>306</v>
-      </c>
+    <row r="133" spans="2:170">
       <c r="B133" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -71071,12 +70676,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:170">
-      <c r="A134" t="s">
-        <v>307</v>
-      </c>
+    <row r="134" spans="2:170">
       <c r="B134" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -71583,12 +71185,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:170">
-      <c r="A135" t="s">
-        <v>308</v>
-      </c>
+    <row r="135" spans="2:170">
       <c r="B135" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -72095,12 +71694,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:170">
-      <c r="A136" t="s">
-        <v>309</v>
-      </c>
+    <row r="136" spans="2:170">
       <c r="B136" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -72607,12 +72203,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:170">
-      <c r="A137" t="s">
-        <v>310</v>
-      </c>
+    <row r="137" spans="2:170">
       <c r="B137" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -73119,12 +72712,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:170">
-      <c r="A138" t="s">
-        <v>311</v>
-      </c>
+    <row r="138" spans="2:170">
       <c r="B138" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -73631,12 +73221,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:170">
-      <c r="A139" t="s">
-        <v>312</v>
-      </c>
+    <row r="139" spans="2:170">
       <c r="B139" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -74143,12 +73730,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:170">
-      <c r="A140" t="s">
-        <v>313</v>
-      </c>
+    <row r="140" spans="2:170">
       <c r="B140" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -74655,12 +74239,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:170">
-      <c r="A141" t="s">
-        <v>314</v>
-      </c>
+    <row r="141" spans="2:170">
       <c r="B141" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -75167,12 +74748,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:170">
-      <c r="A142" t="s">
-        <v>315</v>
-      </c>
+    <row r="142" spans="2:170">
       <c r="B142" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -75679,12 +75257,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:170">
-      <c r="A143" t="s">
-        <v>316</v>
-      </c>
+    <row r="143" spans="2:170">
       <c r="B143" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -76191,12 +75766,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:170">
-      <c r="A144" t="s">
-        <v>317</v>
-      </c>
+    <row r="144" spans="2:170">
       <c r="B144" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -76703,12 +76275,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:170">
-      <c r="A145" t="s">
-        <v>318</v>
-      </c>
+    <row r="145" spans="2:170">
       <c r="B145" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -77215,12 +76784,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:170">
-      <c r="A146" t="s">
-        <v>319</v>
-      </c>
+    <row r="146" spans="2:170">
       <c r="B146" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -77727,12 +77293,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:170">
-      <c r="A147" t="s">
-        <v>320</v>
-      </c>
+    <row r="147" spans="2:170">
       <c r="B147" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -78239,12 +77802,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:170">
-      <c r="A148" t="s">
-        <v>321</v>
-      </c>
+    <row r="148" spans="2:170">
       <c r="B148" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -78751,12 +78311,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:170">
-      <c r="A149" t="s">
-        <v>322</v>
-      </c>
+    <row r="149" spans="2:170">
       <c r="B149" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -79263,12 +78820,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:170">
-      <c r="A150" t="s">
-        <v>323</v>
-      </c>
+    <row r="150" spans="2:170">
       <c r="B150" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -79775,12 +79329,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:170">
-      <c r="A151" t="s">
-        <v>324</v>
-      </c>
+    <row r="151" spans="2:170">
       <c r="B151" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -80287,12 +79838,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:170">
-      <c r="A152" t="s">
-        <v>325</v>
-      </c>
+    <row r="152" spans="2:170">
       <c r="B152" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -80799,12 +80347,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:170">
-      <c r="A153" t="s">
-        <v>326</v>
-      </c>
+    <row r="153" spans="2:170">
       <c r="B153" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -81311,12 +80856,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:170">
-      <c r="A154" t="s">
-        <v>327</v>
-      </c>
+    <row r="154" spans="2:170">
       <c r="B154" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -81823,12 +81365,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:170">
-      <c r="A155" t="s">
-        <v>328</v>
-      </c>
+    <row r="155" spans="2:170">
       <c r="B155" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -82335,12 +81874,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:170">
-      <c r="A156" t="s">
-        <v>329</v>
-      </c>
+    <row r="156" spans="2:170">
       <c r="B156" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -82847,12 +82383,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:170">
-      <c r="A157" t="s">
-        <v>330</v>
-      </c>
+    <row r="157" spans="2:170">
       <c r="B157" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -83359,12 +82892,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:170">
-      <c r="A158" t="s">
-        <v>331</v>
-      </c>
+    <row r="158" spans="2:170">
       <c r="B158" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -83871,12 +83401,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:170">
-      <c r="A159" t="s">
-        <v>332</v>
-      </c>
+    <row r="159" spans="2:170">
       <c r="B159" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -84383,12 +83910,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:170">
-      <c r="A160" t="s">
-        <v>333</v>
-      </c>
+    <row r="160" spans="2:170">
       <c r="B160" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -84895,12 +84419,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:170">
-      <c r="A161" t="s">
-        <v>334</v>
-      </c>
+    <row r="161" spans="2:170">
       <c r="B161" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C161">
         <v>28727400</v>
@@ -85407,12 +84928,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="162" spans="1:170">
-      <c r="A162" t="s">
-        <v>335</v>
-      </c>
+    <row r="162" spans="2:170">
       <c r="B162" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C162">
         <v>28727400</v>
@@ -85919,12 +85437,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:170">
-      <c r="A163" t="s">
-        <v>336</v>
-      </c>
+    <row r="163" spans="2:170">
       <c r="B163" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C163">
         <v>33796940</v>
@@ -86431,12 +85946,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="164" spans="1:170">
-      <c r="A164" t="s">
-        <v>337</v>
-      </c>
+    <row r="164" spans="2:170">
       <c r="B164" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C164">
         <v>45625870</v>
@@ -86943,12 +86455,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:170">
-      <c r="A165" t="s">
-        <v>338</v>
-      </c>
+    <row r="165" spans="2:170">
       <c r="B165" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C165">
         <v>45625870</v>
@@ -87455,12 +86964,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="1:170">
-      <c r="A166" t="s">
-        <v>339</v>
-      </c>
+    <row r="166" spans="2:170">
       <c r="B166" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C166">
         <v>45625870</v>
@@ -87967,12 +87473,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="1:170">
-      <c r="A167" t="s">
-        <v>340</v>
-      </c>
+    <row r="167" spans="2:170">
       <c r="B167" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C167">
         <v>45625870</v>
@@ -88479,12 +87982,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="1:170">
-      <c r="A168" t="s">
-        <v>341</v>
-      </c>
+    <row r="168" spans="2:170">
       <c r="B168" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C168">
         <v>45625870</v>
@@ -88991,12 +88491,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="1:170">
-      <c r="A169" t="s">
-        <v>342</v>
-      </c>
+    <row r="169" spans="2:170">
       <c r="B169" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C169">
         <v>45625870</v>
@@ -89503,12 +89000,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="170" spans="1:170">
-      <c r="A170" t="s">
-        <v>343</v>
-      </c>
+    <row r="170" spans="2:170">
       <c r="B170" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C170">
         <v>45625870</v>
@@ -90015,12 +89509,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="171" spans="1:170">
-      <c r="A171" t="s">
-        <v>344</v>
-      </c>
+    <row r="171" spans="2:170">
       <c r="B171" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C171">
         <v>33796940</v>
@@ -90527,12 +90018,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="172" spans="1:170">
-      <c r="A172" t="s">
-        <v>345</v>
-      </c>
+    <row r="172" spans="2:170">
       <c r="B172" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C172">
         <v>28727400</v>
@@ -91039,12 +90527,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="173" spans="1:170">
-      <c r="A173" t="s">
-        <v>346</v>
-      </c>
+    <row r="173" spans="2:170">
       <c r="B173" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C173">
         <v>10184195908.55</v>
@@ -91551,12 +91036,9 @@
         <v>741</v>
       </c>
     </row>
-    <row r="174" spans="1:170">
-      <c r="A174" t="s">
-        <v>347</v>
-      </c>
+    <row r="174" spans="2:170">
       <c r="B174" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C174">
         <v>25736172</v>
@@ -92063,12 +91545,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:170">
-      <c r="A175" t="s">
-        <v>348</v>
-      </c>
+    <row r="175" spans="2:170">
       <c r="B175" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C175">
         <v>2735827</v>
@@ -92582,35 +92061,34 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" customWidth="1"/>
     <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>349</v>
-      </c>
-      <c r="B1">
+        <v>175</v>
+      </c>
+      <c r="B1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C2">
         <v>8415064562.357</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>350</v>
-      </c>
-      <c r="B2" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>352</v>
-      </c>
-      <c r="B3" t="s">
-        <v>353</v>
       </c>
     </row>
   </sheetData>
@@ -92637,27 +92115,27 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>349</v>
+        <v>177</v>
       </c>
       <c r="C1" t="s">
-        <v>354</v>
+        <v>180</v>
       </c>
       <c r="D1" t="s">
-        <v>355</v>
+        <v>181</v>
       </c>
       <c r="E1" t="s">
-        <v>356</v>
+        <v>182</v>
       </c>
       <c r="F1" t="s">
-        <v>357</v>
+        <v>183</v>
       </c>
       <c r="G1" t="s">
-        <v>358</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -92680,7 +92158,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -92703,7 +92181,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>279382.5</v>
@@ -92726,7 +92204,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>121810770</v>
@@ -92749,7 +92227,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>13156.5</v>
@@ -92772,7 +92250,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>18419100</v>
@@ -92795,7 +92273,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>815832.1949999999</v>
@@ -92818,7 +92296,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>153376452.641</v>
@@ -92841,7 +92319,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>87864</v>
@@ -92864,7 +92342,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11">
         <v>40944624</v>
@@ -92887,7 +92365,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>28324.5</v>
@@ -92910,7 +92388,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>4475271</v>
@@ -92933,7 +92411,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -92956,7 +92434,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -92979,7 +92457,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16">
         <v>31813.5</v>
@@ -93002,7 +92480,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17">
         <v>6967156.5</v>
@@ -93025,7 +92503,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -93048,7 +92526,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -93071,7 +92549,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -93094,7 +92572,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -93117,7 +92595,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -93140,7 +92618,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -93163,7 +92641,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B24">
         <v>72.59999999999999</v>
@@ -93186,7 +92664,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B25">
         <v>4428.6</v>
@@ -93209,7 +92687,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -93232,7 +92710,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -93255,7 +92733,7 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -93278,7 +92756,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -93301,7 +92779,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30">
         <v>113121</v>
@@ -93324,7 +92802,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31">
         <v>130202271</v>
@@ -93347,7 +92825,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -93370,7 +92848,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -93393,7 +92871,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -93416,7 +92894,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -93439,7 +92917,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B36">
         <v>116017.5</v>
@@ -93462,7 +92940,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B37">
         <v>621041677.5</v>
@@ -93485,7 +92963,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -93508,7 +92986,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -93531,7 +93009,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -93554,7 +93032,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -93577,7 +93055,7 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B42">
         <v>30.8</v>
@@ -93600,7 +93078,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B43">
         <v>77000</v>
@@ -93623,7 +93101,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B44">
         <v>27.3</v>
@@ -93646,7 +93124,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B45">
         <v>6497.4</v>
@@ -93669,7 +93147,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -93692,7 +93170,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -93715,7 +93193,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -93738,7 +93216,7 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -93761,7 +93239,7 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -93784,7 +93262,7 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -93807,7 +93285,7 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B52">
         <v>258</v>
@@ -93830,7 +93308,7 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B53">
         <v>403254</v>
@@ -93853,7 +93331,7 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -93876,7 +93354,7 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -93899,7 +93377,7 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -93922,7 +93400,7 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -93945,7 +93423,7 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -93968,7 +93446,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -93991,7 +93469,7 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B60">
         <v>4992</v>
@@ -94014,7 +93492,7 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B61">
         <v>19968000</v>
@@ -94037,7 +93515,7 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -94060,7 +93538,7 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -94083,7 +93561,7 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B64">
         <v>922.9</v>
@@ -94106,7 +93584,7 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B65">
         <v>5537400</v>
@@ -94129,7 +93607,7 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B66">
         <v>1101.1</v>
@@ -94152,7 +93630,7 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B67">
         <v>4954950</v>
@@ -94175,7 +93653,7 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B68">
         <v>957</v>
@@ -94198,7 +93676,7 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B69">
         <v>4306500</v>
@@ -94221,7 +93699,7 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B70">
         <v>12311.2</v>
@@ -94244,7 +93722,7 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B71">
         <v>62516273.6</v>
@@ -94267,7 +93745,7 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B72">
         <v>22</v>
@@ -94290,7 +93768,7 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B73">
         <v>35002</v>
@@ -94313,7 +93791,7 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B74">
         <v>189.8</v>
@@ -94336,7 +93814,7 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B75">
         <v>145576.6</v>
@@ -94359,7 +93837,7 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B76">
         <v>131.3</v>
@@ -94382,7 +93860,7 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B77">
         <v>98475</v>
@@ -94405,7 +93883,7 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B78">
         <v>605.8</v>
@@ -94428,7 +93906,7 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B79">
         <v>3029000</v>
@@ -94451,7 +93929,7 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B80">
         <v>536.9</v>
@@ -94474,7 +93952,7 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B81">
         <v>697970</v>
@@ -94497,7 +93975,7 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B82">
         <v>146.9</v>
@@ -94520,7 +93998,7 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B83">
         <v>282048</v>
@@ -94543,7 +94021,7 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B84">
         <v>37</v>
@@ -94566,7 +94044,7 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B85">
         <v>53983</v>
@@ -94589,7 +94067,7 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B86">
         <v>72783</v>
@@ -94612,7 +94090,7 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B87">
         <v>218349000</v>
@@ -94635,7 +94113,7 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B88">
         <v>686</v>
@@ -94658,7 +94136,7 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B89">
         <v>672280</v>
@@ -94681,7 +94159,7 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B90">
         <v>1</v>
@@ -94704,7 +94182,7 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B91">
         <v>2700</v>
@@ -94727,7 +94205,7 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B92">
         <v>743</v>
@@ -94750,7 +94228,7 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B93">
         <v>713280</v>
@@ -94773,7 +94251,7 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B94">
         <v>172</v>
@@ -94796,7 +94274,7 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B95">
         <v>137600</v>
@@ -94819,7 +94297,7 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B96">
         <v>250</v>
@@ -94842,7 +94320,7 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B97">
         <v>349000</v>
@@ -94865,7 +94343,7 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B98">
         <v>685</v>
@@ -94888,7 +94366,7 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B99">
         <v>1712500</v>
@@ -94911,7 +94389,7 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B100">
         <v>125</v>
@@ -94934,7 +94412,7 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B101">
         <v>250000</v>
@@ -94957,7 +94435,7 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -94980,7 +94458,7 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -95003,7 +94481,7 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B104">
         <v>440</v>
@@ -95026,7 +94504,7 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B105">
         <v>70400</v>
@@ -95049,7 +94527,7 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B106">
         <v>4.8</v>
@@ -95072,7 +94550,7 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B107">
         <v>2400</v>
@@ -95095,7 +94573,7 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B108">
         <v>11</v>
@@ -95118,7 +94596,7 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B109">
         <v>12100</v>
@@ -95141,7 +94619,7 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B110">
         <v>1804</v>
@@ -95164,7 +94642,7 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B111">
         <v>1392688</v>
@@ -95187,7 +94665,7 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -95210,7 +94688,7 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -95233,7 +94711,7 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B114">
         <v>165577.5</v>
@@ -95256,7 +94734,7 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B115">
         <v>45202657.5</v>
@@ -95279,7 +94757,7 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B116">
         <v>1800</v>
@@ -95302,7 +94780,7 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B117">
         <v>1440000</v>
@@ -95325,7 +94803,7 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B118">
         <v>369814.128</v>
@@ -95348,7 +94826,7 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B119">
         <v>51773977.904</v>
@@ -95371,7 +94849,7 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B120">
         <v>6399</v>
@@ -95394,7 +94872,7 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B121">
         <v>16579809</v>
@@ -95417,7 +94895,7 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B122">
         <v>3630</v>
@@ -95440,7 +94918,7 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B123">
         <v>217800</v>
@@ -95463,7 +94941,7 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -95486,7 +94964,7 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -95509,7 +94987,7 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B126">
         <v>152080.5</v>
@@ -95532,7 +95010,7 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B127">
         <v>19314223.5</v>
@@ -95555,7 +95033,7 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B128">
         <v>63194</v>
@@ -95578,7 +95056,7 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B129">
         <v>25656764</v>
@@ -95601,7 +95079,7 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B130">
         <v>19.5</v>
@@ -95624,7 +95102,7 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B131">
         <v>10491</v>
@@ -95647,7 +95125,7 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B132">
         <v>176.07</v>
@@ -95670,7 +95148,7 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B133">
         <v>781398.66</v>
@@ -95693,7 +95171,7 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B134">
         <v>121915.2</v>
@@ -95716,7 +95194,7 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B135">
         <v>204817536</v>
@@ -95739,7 +95217,7 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B136">
         <v>30</v>
@@ -95762,7 +95240,7 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B137">
         <v>24480</v>
@@ -95785,7 +95263,7 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B138">
         <v>1342</v>
@@ -95808,7 +95286,7 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B139">
         <v>271084</v>
@@ -95831,7 +95309,7 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -95854,7 +95332,7 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -95877,7 +95355,7 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -95900,7 +95378,7 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -95923,7 +95401,7 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B144">
         <v>4599</v>
@@ -95946,7 +95424,7 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B145">
         <v>1982169</v>
@@ -95969,7 +95447,7 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -95992,7 +95470,7 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -96015,7 +95493,7 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -96038,7 +95516,7 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -96061,7 +95539,7 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B150">
         <v>5968.5</v>
@@ -96084,7 +95562,7 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B151">
         <v>2148660</v>
@@ -96107,7 +95585,7 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B152">
         <v>2551.9</v>
@@ -96130,7 +95608,7 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B153">
         <v>520587.6</v>
@@ -96153,7 +95631,7 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B154">
         <v>5111975.932</v>
@@ -96176,7 +95654,7 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B155">
         <v>5276081.145</v>
@@ -96199,7 +95677,7 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B156">
         <v>1743766.268</v>
@@ -96222,7 +95700,7 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -96245,7 +95723,7 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -96268,7 +95746,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B159">
         <v>2133207.081</v>
@@ -96291,7 +95769,7 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -96314,7 +95792,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -96337,7 +95815,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B162">
         <v>1329647.415</v>
@@ -96360,7 +95838,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -96383,7 +95861,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B164">
         <v>972742.36</v>
@@ -96406,7 +95884,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B165">
         <v>5756849.869</v>
@@ -96429,7 +95907,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -96452,7 +95930,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B167">
         <v>1050637.457</v>
@@ -96475,7 +95953,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B168">
         <v>1823884.667</v>
@@ -96520,27 +95998,27 @@
         <v>171</v>
       </c>
       <c r="B1" t="s">
-        <v>359</v>
+        <v>185</v>
       </c>
       <c r="C1" t="s">
-        <v>360</v>
+        <v>186</v>
       </c>
       <c r="D1" t="s">
-        <v>355</v>
+        <v>181</v>
       </c>
       <c r="E1" t="s">
-        <v>356</v>
+        <v>182</v>
       </c>
       <c r="F1" t="s">
-        <v>357</v>
+        <v>183</v>
       </c>
       <c r="G1" t="s">
-        <v>361</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -96563,7 +96041,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -96586,7 +96064,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -96609,7 +96087,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -96632,7 +96110,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -96655,7 +96133,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="B7">
         <v>1592.573</v>
@@ -96678,7 +96156,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -96701,7 +96179,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -96724,7 +96202,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="B10">
         <v>262.916</v>
@@ -96747,7 +96225,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B11">
         <v>766.374</v>
@@ -96770,7 +96248,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -96793,7 +96271,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="B13">
         <v>244.706</v>
@@ -96816,7 +96294,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="B14">
         <v>124.44</v>
@@ -96839,7 +96317,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -96862,7 +96340,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="B16">
         <v>162.701</v>
@@ -96885,7 +96363,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -96908,7 +96386,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -96931,7 +96409,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -96954,7 +96432,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="B20">
         <v>1954.462</v>
@@ -96977,7 +96455,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -97000,7 +96478,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -97023,7 +96501,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="B23">
         <v>541.965</v>
@@ -97046,7 +96524,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -97069,7 +96547,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -97092,7 +96570,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="B26">
         <v>515.915</v>
@@ -97115,7 +96593,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -97138,7 +96616,7 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -97161,7 +96639,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="B29">
         <v>857.968</v>
@@ -97184,7 +96662,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="B30">
         <v>206.334</v>
@@ -97207,7 +96685,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -97230,7 +96708,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -97253,7 +96731,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -97276,7 +96754,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="B34">
         <v>2693.989</v>
@@ -97299,7 +96777,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -97322,7 +96800,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -97345,7 +96823,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -97368,7 +96846,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="B38">
         <v>239.128</v>
@@ -97391,7 +96869,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -97414,7 +96892,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="B40">
         <v>3167.815</v>
@@ -97437,7 +96915,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="B41">
         <v>4392.45</v>
@@ -97460,7 +96938,7 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="B42">
         <v>124.926</v>
@@ -97483,7 +96961,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="B43">
         <v>846.1799999999999</v>
@@ -97506,7 +96984,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="B44">
         <v>660.982</v>
@@ -97529,7 +97007,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="B45">
         <v>4448.89</v>
@@ -97552,7 +97030,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="B46">
         <v>2492.158</v>
@@ -97575,7 +97053,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="B47">
         <v>46.092</v>
@@ -97598,7 +97076,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="B48">
         <v>995.578</v>
@@ -97621,7 +97099,7 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="B49">
         <v>2500.338</v>
@@ -97644,7 +97122,7 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="B50">
         <v>1023.102</v>
@@ -97667,7 +97145,7 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="B51">
         <v>2356.062</v>
@@ -97690,7 +97168,7 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="B52">
         <v>1678.301</v>
@@ -97713,7 +97191,7 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="B53">
         <v>1557.934</v>
@@ -97736,7 +97214,7 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="B54">
         <v>4626.909</v>
@@ -97759,7 +97237,7 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="B55">
         <v>2186.528</v>
@@ -97782,7 +97260,7 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="B56">
         <v>106.951</v>
@@ -97805,7 +97283,7 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="B57">
         <v>6226.277</v>
@@ -97828,7 +97306,7 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="B58">
         <v>1216.951</v>
@@ -97851,7 +97329,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -97874,7 +97352,7 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="B60">
         <v>413.679</v>
@@ -97897,7 +97375,7 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -97920,7 +97398,7 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="B62">
         <v>586.2329999999999</v>
@@ -97943,7 +97421,7 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B63">
         <v>4497.961</v>
@@ -97966,7 +97444,7 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -97989,7 +97467,7 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="B65">
         <v>281.055</v>
@@ -98012,7 +97490,7 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="B66">
         <v>29.974</v>
@@ -98035,7 +97513,7 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -98058,7 +97536,7 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="B68">
         <v>3094.451</v>
@@ -98081,7 +97559,7 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="B69">
         <v>91.581</v>
@@ -98104,7 +97582,7 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -98127,7 +97605,7 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="B71">
         <v>216.218</v>
@@ -98150,7 +97628,7 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="B72">
         <v>487.134</v>
@@ -98173,7 +97651,7 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="B73">
         <v>357.666</v>
@@ -98196,7 +97674,7 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="B74">
         <v>704.804</v>
@@ -98219,7 +97697,7 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="B75">
         <v>627.784</v>
@@ -98242,7 +97720,7 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="B76">
         <v>89.78400000000001</v>
@@ -98265,7 +97743,7 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="B77">
         <v>115.907</v>
@@ -98288,7 +97766,7 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -98311,7 +97789,7 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -98334,7 +97812,7 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="B80">
         <v>262.317</v>
@@ -98357,7 +97835,7 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -98380,7 +97858,7 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -98403,7 +97881,7 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="B83">
         <v>220.856</v>
@@ -98426,7 +97904,7 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="B84">
         <v>237.446</v>
@@ -98449,7 +97927,7 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="B85">
         <v>2.73</v>
@@ -98472,7 +97950,7 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="B86">
         <v>2.73</v>
@@ -98495,7 +97973,7 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="B87">
         <v>2.6</v>
@@ -98518,7 +97996,7 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="B88">
         <v>2.5</v>
@@ -98541,7 +98019,7 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="B89">
         <v>2.5</v>
@@ -98564,7 +98042,7 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="B90">
         <v>2.63</v>
@@ -98587,7 +98065,7 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -98610,7 +98088,7 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="B92">
         <v>2.35</v>
@@ -98633,7 +98111,7 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="B93">
         <v>1.1</v>
@@ -98656,7 +98134,7 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="B94">
         <v>2.5</v>
@@ -98679,7 +98157,7 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="B95">
         <v>5.5</v>
@@ -98702,7 +98180,7 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="B96">
         <v>50</v>
@@ -98725,7 +98203,7 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="B97">
         <v>1.3</v>
@@ -98748,7 +98226,7 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="B98">
         <v>0.48</v>
@@ -98771,7 +98249,7 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -98794,7 +98272,7 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -98817,7 +98295,7 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="B101">
         <v>0.3</v>
@@ -98840,7 +98318,7 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="B102">
         <v>0.4</v>
@@ -98863,7 +98341,7 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -98886,7 +98364,7 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="B104">
         <v>1.1</v>
@@ -98909,7 +98387,7 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -98932,7 +98410,7 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="B106">
         <v>15</v>
@@ -98955,7 +98433,7 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="B107">
         <v>3</v>
@@ -98978,7 +98456,7 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="B108">
         <v>1.24</v>
@@ -99001,7 +98479,7 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="B109">
         <v>1.4</v>
@@ -99024,7 +98502,7 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="B110">
         <v>4.75</v>
@@ -99047,7 +98525,7 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="B111">
         <v>4</v>
@@ -99070,7 +98548,7 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="B112">
         <v>4</v>
@@ -99093,7 +98571,7 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="B113">
         <v>4.33</v>
@@ -99116,7 +98594,7 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -99139,7 +98617,7 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -99162,7 +98640,7 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="B116">
         <v>2.3</v>
@@ -99185,7 +98663,7 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="B117">
         <v>2.6</v>
@@ -99208,7 +98686,7 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="B118">
         <v>2.2</v>
@@ -99231,7 +98709,7 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="B119">
         <v>1.7</v>
@@ -99254,7 +98732,7 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="B120">
         <v>2</v>
@@ -99277,7 +98755,7 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="B121">
         <v>15</v>
@@ -99300,7 +98778,7 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="B122">
         <v>10</v>
@@ -99323,7 +98801,7 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="B123">
         <v>0.7</v>
@@ -99346,7 +98824,7 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="B124">
         <v>4</v>
@@ -99369,7 +98847,7 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="B125">
         <v>4</v>
@@ -99392,7 +98870,7 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="B126">
         <v>2</v>
@@ -99415,7 +98893,7 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="B127">
         <v>2.3</v>
@@ -99438,7 +98916,7 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="B128">
         <v>4</v>
@@ -99461,7 +98939,7 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="B129">
         <v>2.2</v>
@@ -99484,7 +98962,7 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="B130">
         <v>8</v>
@@ -99507,7 +98985,7 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="B131">
         <v>6</v>
@@ -99530,7 +99008,7 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="B132">
         <v>2.5</v>
@@ -99553,7 +99031,7 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="B133">
         <v>6</v>
@@ -99576,7 +99054,7 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="B134">
         <v>2.3</v>
@@ -99599,7 +99077,7 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="B135">
         <v>4.25</v>
@@ -99622,7 +99100,7 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="B136">
         <v>10</v>
@@ -99645,7 +99123,7 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="B137">
         <v>10</v>
@@ -99668,7 +99146,7 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="B138">
         <v>3</v>
@@ -99691,7 +99169,7 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="B139">
         <v>15</v>
@@ -99714,7 +99192,7 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -99737,7 +99215,7 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="B141">
         <v>2</v>
@@ -99760,7 +99238,7 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="B142">
         <v>0.6</v>
@@ -99783,7 +99261,7 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="B143">
         <v>19.5</v>
@@ -99806,7 +99284,7 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="B144">
         <v>2.5</v>
@@ -99829,7 +99307,7 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="B145">
         <v>15</v>
@@ -99852,7 +99330,7 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="B146">
         <v>7.547</v>
@@ -99875,7 +99353,7 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="B147">
         <v>6.5</v>
@@ -99898,7 +99376,7 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="B148">
         <v>6</v>
@@ -99921,7 +99399,7 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -99944,7 +99422,7 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="B150">
         <v>1.2</v>
@@ -99967,7 +99445,7 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="B151">
         <v>1.6</v>
@@ -99990,7 +99468,7 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="B152">
         <v>3</v>
@@ -100013,7 +99491,7 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="B153">
         <v>1.3</v>
@@ -100036,7 +99514,7 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="B154">
         <v>5.5</v>
@@ -100059,7 +99537,7 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="B155">
         <v>8.109999999999999</v>
@@ -100082,7 +99560,7 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="B156">
         <v>2.35</v>
@@ -100105,7 +99583,7 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="B157">
         <v>7</v>
@@ -100128,7 +99606,7 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="B158">
         <v>8.109999999999999</v>
@@ -100151,7 +99629,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="B159">
         <v>2.63</v>
@@ -100174,7 +99652,7 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="B160">
         <v>6.3</v>
@@ -100197,7 +99675,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="B161">
         <v>19.717</v>
@@ -100220,7 +99698,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="B162">
         <v>19.717</v>
@@ -100243,7 +99721,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="B163">
         <v>19.717</v>
@@ -100266,7 +99744,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -100289,7 +99767,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -100312,7 +99790,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="B166">
         <v>19.717</v>
@@ -100335,7 +99813,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="B167">
         <v>18.057</v>
@@ -100358,7 +99836,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -100381,7 +99859,7 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="B169">
         <v>19.717</v>
@@ -100404,7 +99882,7 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="B170">
         <v>17.912</v>
@@ -100427,7 +99905,7 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="B171">
         <v>19.717</v>
@@ -100450,7 +99928,7 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="B172">
         <v>19.717</v>
@@ -100473,7 +99951,7 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="B173">
         <v>0.052</v>
@@ -100496,7 +99974,7 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -100519,7 +99997,7 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="B175">
         <v>277.862</v>
